--- a/artfynd/A 2409-2022 artfynd.xlsx
+++ b/artfynd/A 2409-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2409-2022 artfynd.xlsx
+++ b/artfynd/A 2409-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>98428869</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563493.1165041686</v>
+        <v>563493</v>
       </c>
       <c r="R2" t="n">
-        <v>6686828.781346513</v>
+        <v>6686829</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98428873</v>
+        <v>98529243</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,17 +810,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Garpenberg , Dlr</t>
+          <t>Garpenberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563449.5785944132</v>
+        <v>563490</v>
       </c>
       <c r="R3" t="n">
-        <v>6686791.843968838</v>
+        <v>6686805</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98529218</v>
+        <v>98529249</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563444.4346869264</v>
+        <v>563496</v>
       </c>
       <c r="R4" t="n">
-        <v>6686802.162047381</v>
+        <v>6686796</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,19 +948,9 @@
           <t>2022-02-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,57 +978,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98529231</v>
+        <v>98428873</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Garpenberg, Dlr</t>
+          <t>Garpenberg , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563376.5726252031</v>
+        <v>563449</v>
       </c>
       <c r="R5" t="n">
-        <v>6686879.285179445</v>
+        <v>6686792</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98529243</v>
+        <v>98529201</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563489.5521619589</v>
+        <v>563496</v>
       </c>
       <c r="R6" t="n">
-        <v>6686805.426016336</v>
+        <v>6686885</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1142,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Hedemora</t>
+          <t>Garpenberg</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1216,19 +1150,9 @@
           <t>2022-02-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98529236</v>
+        <v>98529218</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563404.0346007693</v>
+        <v>563444</v>
       </c>
       <c r="R7" t="n">
-        <v>6686841.602278193</v>
+        <v>6686802</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1332,19 +1251,9 @@
           <t>2022-02-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,43 +1281,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98529192</v>
+        <v>98529236</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1416,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563474.098722597</v>
+        <v>563404</v>
       </c>
       <c r="R8" t="n">
-        <v>6686809.121562488</v>
+        <v>6686842</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1449,19 +1352,9 @@
           <t>2022-02-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98529226</v>
+        <v>98529192</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563394.6535232405</v>
+        <v>563474</v>
       </c>
       <c r="R9" t="n">
-        <v>6686867.209954998</v>
+        <v>6686809</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1566,19 +1454,9 @@
           <t>2022-02-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,15 +1484,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98647071</v>
+        <v>98529195</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563358.5987220044</v>
+        <v>563496</v>
       </c>
       <c r="R10" t="n">
-        <v>6686856.670879243</v>
+        <v>6686885</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,27 +1548,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Hedemora</t>
+          <t>Garpenberg</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,6 +1583,312 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>98529226</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Garpenberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563395</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6686867</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>98529231</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Garpenberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563377</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6686879</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>98647071</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Garpenberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563359</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6686857</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2409-2022 artfynd.xlsx
+++ b/artfynd/A 2409-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98428869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529243</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529249</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98428873</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529201</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529218</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529236</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529192</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529195</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529226</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98529231</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,8 +1949,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98647071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>